--- a/Mod_Korean/Lang/KR/Game/Recipe.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Recipe.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="99">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -26,220 +26,223 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
+    <t xml:space="preserve">EA 23.352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha 19.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.325</t>
+  </si>
+  <si>
     <t xml:space="preserve">EA 23.338 Patch 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha 19.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.325</t>
   </si>
   <si>
     <t xml:space="preserve">Alpha 20.7</t>
@@ -456,7 +459,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13">
@@ -472,7 +475,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15">
@@ -480,7 +483,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>3</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16">
@@ -488,7 +491,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17">
@@ -496,7 +499,7 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -504,7 +507,7 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19">
@@ -512,7 +515,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20">
@@ -520,7 +523,7 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21">
@@ -528,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22">
@@ -536,7 +539,7 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23">
@@ -544,7 +547,7 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24">
@@ -552,7 +555,7 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25">
@@ -560,7 +563,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26">
@@ -568,7 +571,7 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27">
@@ -576,7 +579,7 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28">
@@ -584,7 +587,7 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29">
@@ -592,7 +595,7 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30">
@@ -600,7 +603,7 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31">
@@ -608,7 +611,7 @@
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32">
@@ -616,7 +619,7 @@
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33">
@@ -624,7 +627,7 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34">
@@ -632,7 +635,7 @@
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35">
@@ -640,7 +643,7 @@
         <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36">
@@ -648,7 +651,7 @@
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37">
@@ -664,7 +667,7 @@
         <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39">
@@ -688,7 +691,7 @@
         <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42">
@@ -704,7 +707,7 @@
         <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44">
@@ -744,7 +747,7 @@
         <v>48</v>
       </c>
       <c r="B48" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="49">
@@ -752,7 +755,7 @@
         <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="50">
@@ -760,7 +763,7 @@
         <v>50</v>
       </c>
       <c r="B50" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51">
@@ -824,7 +827,7 @@
         <v>58</v>
       </c>
       <c r="B58" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="59">
@@ -832,7 +835,7 @@
         <v>59</v>
       </c>
       <c r="B59" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="60">
@@ -840,7 +843,7 @@
         <v>60</v>
       </c>
       <c r="B60" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="61">
@@ -848,7 +851,7 @@
         <v>61</v>
       </c>
       <c r="B61" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="62">
@@ -856,7 +859,7 @@
         <v>62</v>
       </c>
       <c r="B62" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="63">
@@ -864,7 +867,7 @@
         <v>63</v>
       </c>
       <c r="B63" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="64">
@@ -872,7 +875,7 @@
         <v>64</v>
       </c>
       <c r="B64" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="65">
@@ -880,7 +883,7 @@
         <v>65</v>
       </c>
       <c r="B65" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="66">
@@ -888,7 +891,7 @@
         <v>66</v>
       </c>
       <c r="B66" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="67">
@@ -896,7 +899,7 @@
         <v>67</v>
       </c>
       <c r="B67" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="68">
@@ -904,7 +907,7 @@
         <v>68</v>
       </c>
       <c r="B68" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="69">
@@ -912,7 +915,7 @@
         <v>69</v>
       </c>
       <c r="B69" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="70">
@@ -920,7 +923,7 @@
         <v>70</v>
       </c>
       <c r="B70" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="71">
@@ -928,7 +931,7 @@
         <v>71</v>
       </c>
       <c r="B71" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="72">
@@ -936,7 +939,7 @@
         <v>72</v>
       </c>
       <c r="B72" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/Mod_Korean/Lang/KR/Game/Recipe.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Recipe.xlsx
@@ -26,7 +26,7 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.352</t>
+    <t xml:space="preserve">EA 23.355</t>
   </si>
   <si>
     <t xml:space="preserve">2</t>
